--- a/Luban/Config/Datas/#ItemConfig.xlsx
+++ b/Luban/Config/Datas/#ItemConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62E5EDB0-293A-4C7D-ADD7-7C7B36D8E3A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D56128D6-A7F4-42BF-84E9-867A79422C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="5340" yWindow="4800" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -115,7 +115,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -130,6 +130,19 @@
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -154,9 +167,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -472,105 +491,110 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="6" max="6" width="41.25" customWidth="1"/>
+    <col min="1" max="5" width="9" style="2"/>
+    <col min="6" max="6" width="41.25" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B4">
+      <c r="B4" s="2">
         <v>1001</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="2">
         <v>10</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B5">
+      <c r="B5" s="2">
         <v>1002</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="2">
         <v>100</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="2" t="s">
         <v>19</v>
       </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F12" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
